--- a/Dataset/3_label/OPENING_OPENING_V1_0.5 divisions_per_second.xlsx
+++ b/Dataset/3_label/OPENING_OPENING_V1_0.5 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:D320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6138,6 +6138,60 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>65400</v>
+      </c>
+      <c r="C318" t="n">
+        <v>70</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>65600</v>
+      </c>
+      <c r="C319" t="n">
+        <v>70</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>65800</v>
+      </c>
+      <c r="C320" t="n">
+        <v>70</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
